--- a/Result/profitability/3046.xlsx
+++ b/Result/profitability/3046.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.1</v>
       </c>
       <c r="M2" t="n">
-        <v>0.89375</v>
+        <v>0.9312500000000001</v>
       </c>
       <c r="N2" t="n">
-        <v>9.45875</v>
+        <v>9.620000000000001</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>0.09</v>
       </c>
       <c r="M3" t="n">
-        <v>0.7487500000000001</v>
+        <v>0.86875</v>
       </c>
       <c r="N3" t="n">
-        <v>11.805</v>
+        <v>11.94875</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>0.19</v>
       </c>
       <c r="M4" t="n">
-        <v>0.69875</v>
+        <v>0.7537499999999999</v>
       </c>
       <c r="N4" t="n">
-        <v>13.94625</v>
+        <v>14</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>-0.11</v>
       </c>
       <c r="M5" t="n">
-        <v>0.54625</v>
+        <v>0.64</v>
       </c>
       <c r="N5" t="n">
-        <v>16.16375</v>
+        <v>16.1425</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>0.02</v>
       </c>
       <c r="M6" t="n">
-        <v>0.44875</v>
+        <v>0.465</v>
       </c>
       <c r="N6" t="n">
-        <v>18.79375</v>
+        <v>18.69125</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>0.08</v>
       </c>
       <c r="M7" t="n">
-        <v>0.28125</v>
+        <v>0.39</v>
       </c>
       <c r="N7" t="n">
-        <v>20.84125</v>
+        <v>20.9225</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>0.09</v>
       </c>
       <c r="M8" t="n">
-        <v>0.2075</v>
+        <v>0.25125</v>
       </c>
       <c r="N8" t="n">
-        <v>23.52</v>
+        <v>23.44125</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -9830,6 +9830,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>3046</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>2474</v>
+      </c>
+      <c r="D75" t="n">
+        <v>2265</v>
+      </c>
+      <c r="E75" t="n">
+        <v>209</v>
+      </c>
+      <c r="F75" t="n">
+        <v>8.44</v>
+      </c>
+      <c r="G75" t="n">
+        <v>139</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>5.63%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>9</v>
+      </c>
+      <c r="J75" t="n">
+        <v>149</v>
+      </c>
+      <c r="K75" t="n">
+        <v>122</v>
+      </c>
+      <c r="L75" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="M75" t="n">
+        <v>1.075</v>
+      </c>
+      <c r="N75" t="n">
+        <v>8.202500000000001</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>1</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.3500000000000001</v>
+      </c>
+      <c r="X75" t="n">
+        <v>0.2916666666666667</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-0.6300000000000008</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.06945975744211697</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>0.9375</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-0.1699999999999999</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.01974448315911725</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
